--- a/Hardware/接腳.xlsx
+++ b/Hardware/接腳.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y1032\Documents\專題\總程式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y1032\Documents\GitHub\Centralized-mobile-phone-management-system\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD2EE0F-4952-41C7-8A61-EF3FA84B82DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEEFF3D-7A1F-4AB5-B8ED-B542E18A881A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,19 +150,63 @@
     <t>Mega TX</t>
   </si>
   <si>
-    <t>RX2 (串列接收)</t>
-  </si>
-  <si>
     <t>GPIO 27</t>
   </si>
   <si>
     <t>Mega RX</t>
   </si>
   <si>
-    <t>TX2 (串列發送)</t>
-  </si>
-  <si>
     <t>MQ-135</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mega 2560 RX2 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>串列接收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mega 2560 TX2 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>串列發送</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +241,13 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -541,7 +592,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -679,7 +730,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="41.45" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="70" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -687,18 +738,18 @@
         <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="70" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="41.45" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
